--- a/data_extactor/batch_10_fa/batch_0064_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0064_fa.xlsx
@@ -508,27 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | درک نوشته‌ها | گوش دادن فعالانه | تفکر انتقادی | نگارش | یادگیری فعالانه | پایش</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | امور اداری | رایانه‌ها و الکترونیک | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | اداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشته‌ها | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | بینایی دور | سازماندهی اطلاعات | استدلال استقرایی | اصالت | انعطاف‌پذیری بستار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | بینایی دور | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | ایمیل | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیمی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت نشسته | اهمیت دقیق بودن یا بی‌نقص بودن | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | محیط‌های داخلی و دارای کنترل دما</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Architects, Except Landscape and Naval | Architectural and Engineering Managers | Construction Managers | Cost Estimators | Electrical Engineers | Energy Auditors | Energy Engineers, Except Wind and Solar | Geothermal Production Managers | Sales Engineers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Solar Energy Installation Managers | Solar Energy Systems Engineers | Solar Photovoltaic Installers | Solar Thermal Installers and Technicians | Sustainability Specialists | Wind Energy Development Managers | Wind Energy Engineers | Wind Energy Operations Managers | Wind Turbine Service Technicians</t>
+          <t>معماران، به‌جز منظر و دریایی | مدیران معماری و مهندسی | مدیران ساخت‌وساز | برآوردکنندگان هزینه | مهندسان برق | بازرسان انرژی | مهندسان انرژی، به جز باد و خورشید | مدیران تولید زمین‌گرمایی | مهندسان فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | متخصصان پایداری | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی | تکنسین‌های خدمات توربین بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3M Post-it App | ACT! Premium | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Advantage Signature Marketing Group Web Master | Airtable | Apache Groovy | Apple Keynote | Apple macOS | Aptean Onyx CRM | Ardexus Mode | Ardexus TASC | Autodesk AutoCAD | نرم‌افزار Blackboard | Blink | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Commence Application Suite | تقویم‌های تماس رایانه‌ای | سیستم‌های مدیریت زمان رایانه‌ای | سیستم‌های مدیریت مخاطبین | Contract Central | نرم‌افزار پیگیری قرارداد | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Epic Systems | Evernote | زبان نشانه‌گذاری گسترش‌پذیر XML | FaceTime | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Analytics | Google Classroom | Google Docs | Google Drive | Google Meet | Google Slides | GroupMe | HEAT Software GoldMine | نرم‌افزار دستگاه‌های رایانه‌ای دستی | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | نرم‌افزار HubSpot | HydraNet | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Intuit QuickBooks | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MASterMind | Marketo Marketing Automation | Maximizer Software Maximizer Enterprise | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics CRM | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Mozilla Firefox | Mozilla Thunderbird | NetSuite ERP | NetSuite NetCRM | نرم‌افزار امنیت سایبری NortonLifeLock | Novo Customer Tracking Software | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle WebLogic Server | Qlik Tech QlikView | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Relavis CRM Portal | Root Systems SPS Process Management | SAP Business Objects | نرم‌افزار SAP | SAS | SSA Global BPCS | Sage 50 Accounting | Sage SalesLogix | نرم‌افزار اتوماسیون نیروی فروش | SalesInSync | نرم‌افزار Salesforce | SamePage StudioCRM | Screencastify | SeaMonkey | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Soffront CRM Portal | Tableau | نرم‌افزار مالیات | Tigerpaw | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار Yardi | YouTube | Zoom | interlinkONE | vtiger CRM</t>
+          <t>3M Post-it App | ACT! Premium | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Advantage Signature Marketing Group Web Master | Airtable | Apache Groovy | Apple Keynote | Apple macOS | Aptean Onyx CRM | Ardexus Mode | Ardexus TASC | Autodesk AutoCAD | نرم‌افزار Blackboard | Blink | Cisco Webex | نرم‌افزار رایانش ابری Citrix | Commence Application Suite | تقویم‌های تماس رایانه‌ای | سیستم‌های مدیریت زمان رایانه‌ای | سیستم‌های مدیریت مخاطبین | Contract Central | نرم‌افزار پیگیری قرارداد | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Delphi Technology | Dropbox | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eko | Epic Systems | Evernote | زبان نشانه‌گذاری توسعه‌پذیر XML | FaceTime | Facebook | FileMaker Pro | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Analytics | Google Classroom | Google Docs | Google Drive | Google Meet | Google Slides | GroupMe | HEAT Software GoldMine | نرم‌افزار دستگاه‌های کامپیوتر جیبی | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار HubSpot | HydraNet | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Intuit QuickBooks | LexisNexis | LinkedIn | LogMeIn GoToMeeting | LogMeIn GoToWebinar | MASterMind | Marketo Marketing Automation | Maximizer Software Maximizer Enterprise | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics CRM | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | Mozilla Firefox | Mozilla Thunderbird | NetSuite ERP | NetSuite NetCRM | نرم‌افزار امنیت سایبری NortonLifeLock | Novo Customer Tracking Software | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle WebLogic Server | Qlik Tech QlikView | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | Relavis CRM Portal | Root Systems SPS Process Management | SAP Business Objects | نرم‌افزار SAP | SAS | SSA Global BPCS | Sage 50 Accounting | Sage SalesLogix | نرم‌افزار اتوماسیون نیروی فروش | SalesInSync | نرم‌افزار Salesforce | SamePage StudioCRM | Screencastify | SeaMonkey | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Soffront CRM Portal | Tableau | نرم‌افزار مالیاتی | Tigerpaw | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار Yardi | YouTube | Zoom | interlinkONE | vtiger CRM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | گوش دادن فعالانه | تفکر انتقادی | درک نوشته‌ها | نگارش | یادگیری فعالانه | پایش</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و شخصی | زبان انگلیسی | ریاضیات | حمل‌ونقل | رایانه‌ها و الکترونیک</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک نوشته‌ها | تشخیص گفتار | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری طبقه‌بندی | سازماندهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال استقرایی | اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | گفتگوهای تلفنی | برخورد با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیمی | ایمیل | فراوانی تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | محیط‌های داخلی و دارای کنترل دما | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | فشار زمانی | اهمیت دقیق بودن یا بی‌نقص بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | فشار زمانی | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Buyers and Purchasing Agents, Farm Products | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Logisticians | Procurement Clerks | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Purchasing Managers | Retail Salespersons | Sales Engineers | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Supply Chain Managers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>نمایندگان فروش تبلیغات | خریداران و نمایندگان خرید، محصولات کشاورزی | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | لجستیسین‌ها | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | مدیران زنجیره تأمین | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن‌ورزی | درک نوشته‌ها | تفکر انتقادی | نگارش | پایش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | زبان انگلیسی | تولید مواد غذایی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | تولید مواد غذایی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | سازماندهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک نوشته‌ها</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | صرف زمان به صورت ایستاده | برخورد با مشتریان خارجی یا عموم مردم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | محیط‌های داخلی و دارای کنترل دما | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیمی | فشار زمانی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | ایمیل | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ارتباط با دیگران | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | ایمیل | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | Driver/Sales Workers | First-Line Supervisors of Non-Retail Sales Workers | First-Line Supervisors of Retail Sales Workers | Hosts and Hostesses, Restaurant, Lounge, and Coffee Shop | Marketing Managers | Meeting, Convention, and Event Planners | Merchandise Displayers and Window Trimmers | Parts Salespersons | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>نمایندگان فروش تبلیغات | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | رانندگان توزیع و فروشندگان | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان فروش خرده‌فروشی | میزبانان رستوران، سالن و کافی‌شاپ | مدیران بازاریابی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | فروشندگان قطعات | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Apple Safari | Apple iOS | Facebook | Instagram | LinkedIn | Microsoft Excel | Microsoft Office software | Microsoft PowerPoint | Microsoft Word | Tumblr | Twitter | نرم‌افزار مرورگر وب | YouTube</t>
+          <t>Apple Safari | Apple iOS | Facebook | Instagram | LinkedIn | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | Tumblr | Twitter | نرم‌افزار مرورگر وب | YouTube</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن‌ورزی | پایش | تفکر انتقادی | درک نوشته‌ها</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | ارتباطات و رسانه | هنرهای زیبا | زبان انگلیسی | بازاریابی و فروش | طراحی</t>
+          <t>خدمات مشتری و شخصی | ارتباطات و رسانه | هنرهای زیبا | زبان انگلیسی | فروش و بازاریابی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | بینایی دور | هماهنگی کلی بدن | تعادل کلی بدن | استقامت | انعطاف‌پذیری حرکتی | حفظ کردن | حساسیت به مسئله | اصالت | سازماندهی اطلاعات | تشخیص گفتار | توجه انتخابی | هماهنگی چند عضو | قدرت تنه | انعطاف‌پذیری پویا</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | بینایی دور | هماهنگی کلی بدن | تعادل کلی بدن | استقامت | انعطاف‌پذیری دامنه حرکت | حفظ کردن | حساسیت به مسئله | اصالت | ترتیب‌دهی اطلاعات | تشخیص گفتار | توجه انتخابی | هماهنگی چند عضو | قدرت تنه | انعطاف‌پذیری پویا</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>محیط‌های داخلی و دارای کنترل دما | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Actors | Art Directors | Camera Operators, Television, Video, and Film | Camera and Photographic Equipment Repairers | Costume Attendants | Craft Artists | Dancers | Demonstrators and Product Promoters | Fashion Designers | Fine Artists, Including Painters, Sculptors, and Illustrators | Graphic Designers | Makeup Artists, Theatrical and Performance | Merchandise Displayers and Window Trimmers | Model Makers, Wood | Painting, Coating, and Decorating Workers | Photographers | Photographic Process Workers and Processing Machine Operators | Set and Exhibit Designers | Special Effects Artists and Animators | Talent Directors</t>
+          <t>بازیگران | مدیران هنری | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | متصدیان لباس | هنرمندان صنایع دستی | رقصندگان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | طراحان مد | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | میکاپ آرتیست‌های تئاتر و نمایش | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | مدل‌سازان چوب | کارگران نقاشی، پوشش‌دهی و تزیین | عکاسان | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | طراحان صحنه و نمایشگاه | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران استعداد</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | تفکر انتقادی | درک نوشته‌ها | گوش دادن فعالانه | یادگیری فعالانه | نگارش | پایش</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و شخصی | زبان انگلیسی | قانون و دولت | مدیریت و سازماندهی | اقتصاد و حسابداری | رایانه‌ها و الکترونیک | ریاضیات | ارتباطات و رسانه | ساختمان و ساخت‌وساز | امور اداری | آموزش و پرورش | روان‌شناسی</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشته‌ها | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | سازماندهی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | محیط‌های داخلی و دارای کنترل دما | ارتباط با دیگران | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | سطح رقابت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیمی | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق بودن یا بی‌نقص بودن | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط‌های بیرونی، در معرض تمام شرایط آب‌وهوایی | صرف زمان به صورت نشسته</t>
+          <t>ایمیل | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | سطح رقابت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Appraisers and Assessors of Real Estate | Appraisers of Personal and Business Property | Brokerage Clerks | Counter and Rental Clerks | Credit Analysts | Credit Authorizers, Checkers, and Clerks | Credit Counselors | Financial and Investment Analysts | Insurance Sales Agents | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Property, Real Estate, and Community Association Managers | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Real Estate Sales Agents | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | کارمندان کارگزاری | کارمندان باجه و اجاره | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | مدیران املاک، مستغلات و انجمن‌های اجتماعی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | نمایندگان فروش املاک | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Agent Business Builder | Argosy Legal Systems Power Closer | CMA Stuffers | Canva | نرم‌افزار تحلیل هزینه پروژه توسعه تجاری و صنعتی | Corel WordPerfect Office Suite | DataBasix Technologies Lead Commander | DeLorme Topo USA | نرم‌افزار قرارداد دیجیتال | DocuSign eSignature | نرم‌افزار ایجاد سند | Easypano Tourweaver | نرم‌افزار ایمیل | FaceTime | Facebook | نرم‌افزار ماشین‌حساب‌های مالی | FloodMaps | Front Desk | نرم‌افزار حسابداری صندوق | Garmin City Select | General Magic Portico | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Docs | Google Drive | Greenbrier Graphics Deed Plotter | نرم‌افزار HUD-1 | نرم‌افزار رتبه‌بندی خانه | IBM Lotus 1-2-3 | In-Hand Pocket APOD | نرم‌افزار پایگاه داده MLS مبتنی بر اینترنت | Intuit QuickBooks | Iseemedia Photovista Panorama | Landlord Software Pro Flipper | LinkedIn | نرم‌افزار پردازش درخواست وام | Loom | Lucero System Office Management | MediaVue | Microsoft Dynamics | Microsoft Excel | Microsoft FrontPage | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Teams | Microsoft Word | Moxi Works MoxiEngage | Moxi Works MoxiImpress | Moxi Works MoxiPresent | پایگاه داده آنلاین انجمن ملی مشاوران املاک | نرم‌افزار ناوبری | نرم‌افزار تولید خبرنامه | OWL Bookkeeping for Realtors | Panorama Technologies ModelWeaver | Panoweaver Panorama | Power Real Estate Letters | PrimaSoft PC Realtor Organizer Deluxe | ProForce Highlight Flyer Master | ProForce Ultimate Brochures | RPIS Silent Flyer | Real Pro | نرم‌افزار انتقال قرارداد برنامه املاک REACT | نرم‌افزار تحلیل سرمایه‌گذاری املاک | RealData Comparative Lease Analysis | Reality Star ProAGENT Power Series Presentations | Realtors Property Resource RPR | RealtyStar AgentOffice | RealtyStar Real Estate Assistant | Reveal Systems Truewire | SRC Cash Flow Analyzer Pro | نرم‌افزار زمان‌بندی | Showing Suite HomeFeedback | Showing Suite HomeFollowup | Showing Suite Showing Calendar | Showing Suite real estate software | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مالیات | Telluride Software Classic Trak-It | The IPIX Real Estate Wizard hometour360 Wizard | نرم‌افزار TimeValue | TopProducer | Topaz Software Symplifi (ویژگی CRM) | Topaz Software Symplifi (ویژگی تحلیل کسب‌وکار) | پایگاه‌های داده تحت وب | Wheatworks Real Estate Calculator Suite | Xactware Xactimate | Yardi Systems Yardi Enterprise | نرم‌افزار Yardi | Zoom | eGrabber ListGrabber | iKorb Real Estate</t>
+          <t>Adobe Acrobat | Agent Business Builder | Argosy Legal Systems Power Closer | CMA Stuffers | Canva | نرم‌افزار تحلیل هزینه پروژه توسعه تجاری و صنعتی | Corel WordPerfect Office Suite | DataBasix Technologies Lead Commander | DeLorme Topo USA | نرم‌افزار قرارداد دیجیتال | DocuSign eSignature | نرم‌افزار ایجاد سند | Easypano Tourweaver | نرم‌افزار ایمیل | FaceTime | Facebook | نرم‌افزار ماشین‌حساب‌های مالی | FloodMaps | Front Desk | نرم‌افزار حسابداری صندوق | Garmin City Select | General Magic Portico | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Google Ads | Google Docs | Google Drive | Greenbrier Graphics Deed Plotter | نرم‌افزار HUD-1 | نرم‌افزار رتبه‌بندی خانه | IBM Lotus 1-2-3 | In-Hand Pocket APOD | نرم‌افزار پایگاه داده MLS مبتنی بر اینترنت | Intuit QuickBooks | Iseemedia Photovista Panorama | Landlord Software Pro Flipper | LinkedIn | نرم‌افزار پردازش درخواست وام | Loom | Lucero System Office Management | MediaVue | Microsoft Dynamics | Microsoft Excel | Microsoft FrontPage | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft Teams | Microsoft Word | Moxi Works MoxiEngage | Moxi Works MoxiImpress | Moxi Works MoxiPresent | پایگاه داده آنلاین انجمن ملی مشاوران املاک | نرم‌افزار ناوبری | نرم‌افزار تولید خبرنامه | OWL Bookkeeping for Realtors | Panorama Technologies ModelWeaver | Panoweaver Panorama | Power Real Estate Letters | PrimaSoft PC Realtor Organizer Deluxe | ProForce Highlight Flyer Master | ProForce Ultimate Brochures | RPIS Silent Flyer | Real Pro | نرم‌افزار انتقال قرارداد برنامه املاک REACT | نرم‌افزار تحلیل سرمایه‌گذاری املاک | RealData Comparative Lease Analysis | Reality Star ProAGENT Power Series Presentations | Realtors Property Resource RPR | RealtyStar AgentOffice | RealtyStar Real Estate Assistant | Reveal Systems Truewire | SRC Cash Flow Analyzer Pro | نرم‌افزار زمان‌بندی | Showing Suite HomeFeedback | Showing Suite HomeFollowup | Showing Suite Showing Calendar | Showing Suite real estate software | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مالیاتی | Telluride Software Classic Trak-It | The IPIX Real Estate Wizard hometour360 Wizard | نرم‌افزار TimeValue | TopProducer | Topaz Software Symplifi (ویژگی CRM) | Topaz Software Symplifi (ویژگی تحلیل کسب‌وکار) | پایگاه‌های داده تحت وب | Wheatworks Real Estate Calculator Suite | Xactware Xactimate | Yardi Systems Yardi Enterprise | نرم‌افزار Yardi | Zoom | eGrabber ListGrabber | iKorb Real Estate</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | گوش دادن فعالانه | تفکر انتقادی | درک نوشته‌ها | نگارش | یادگیری فعالانه | ریاضیات | پایش</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | زبان انگلیسی | قانون و دولت | امور اداری | مدیریت و سازماندهی | ریاضیات | رایانه‌ها و الکترونیک | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اقتصاد و حسابداری | آموزش و پرورش | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | قانون و دولت | اداری | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اقتصاد و حسابداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک نوشته‌ها | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری طبقه‌بندی | سازماندهی اطلاعات | استدلال استقرایی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بینایی نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | ارتباط با دیگران | گفتگوهای تلفنی | سطح رقابت | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق بودن یا بی‌نقص بودن | محیط‌های داخلی و دارای کنترل دما | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیمی</t>
+          <t>ایمیل | ارتباط با دیگران | مکالمات تلفنی | سطح رقابت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فشار زمانی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Appraisers and Assessors of Real Estate | Appraisers of Personal and Business Property | Brokerage Clerks | Counter and Rental Clerks | Credit Counselors | Financial and Investment Analysts | Insurance Sales Agents | Loan Interviewers and Clerks | Loan Officers | New Accounts Clerks | Personal Financial Advisors | Property, Real Estate, and Community Association Managers | Purchasing Agents, Except Wholesale, Retail, and Farm Products | Real Estate Brokers | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Securities, Commodities, and Financial Services Sales Agents | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>نمایندگان فروش تبلیغات | ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | کارمندان کارگزاری | کارمندان باجه و اجاره | مشاوران اعتبار | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | مدیران املاک، مستغلات و انجمن‌های اجتماعی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | کارگزاران املاک | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ab Initio | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Cassandra | Apache HBase | Apache Hadoop | Apache Pig | Apache Struts | Apple iOS | Atlassian JIRA | Autodesk AutoCAD | پروتکل دروازه مرزی BGP | C | C++ | Cisco Systems CiscoWorks | Cisco Systems VPN Client | نرم‌افزار رایانش ابری Citrix | Dassault Systemes SolidWorks | نرم‌افزار مدیریت پایگاه داده | Docker | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | زبان نشانه‌گذاری ابرمتن گسترش‌پذیر XHTML | زبان نشانه‌گذاری گسترش‌پذیر XML | نرم‌افزار فایروال | نرم‌افزار Google Cloud | نرم‌افزار Google Workspace | نرم‌افزار گرافیک | Hewlett Packard HP-UX | Hyperion Solutions Hyperion System 9 Bi+ | IBM Cognos Business Intelligence | IBM Cognos Impromptu | IBM DB2 | IBM Domino | Informatica Corporation PowerCenter | JavaScript | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار کلان‌داده MapReduce | McAfee | MicroStrategy | MicroStrategy Desktop | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office Live Meeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows Server | Microsoft Word | نرم‌افزار خدمات دایرکتوری شبکه | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle Java | Oracle PeopleSoft | Oracle Solaris | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Python | R | RESTful API | React | Ruby | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Business One | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | نرم‌افزار تحلیل فروش | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی | زبان نشانه‌گذاری تایید امنیت SAML | Shell script | ورود یکپارچه SSO | نرم‌افزار به عنوان سرویس SaaS | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | Teradata Database | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | WebEx Sales Center | Wireshark</t>
+          <t>Ab Initio | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Cassandra | Apache HBase | Apache Hadoop | Apache Pig | Apache Struts | Apple iOS | Atlassian JIRA | Autodesk AutoCAD | پروتکل مسیریابی مرزی BGP | C | C++ | Cisco Systems CiscoWorks | Cisco Systems VPN Client | نرم‌افزار رایانش ابری Citrix | Dassault Systemes SolidWorks | نرم‌افزار مدیریت پایگاه داده | Docker | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار فایروال | نرم‌افزار Google Cloud | نرم‌افزار Google Workspace | نرم‌افزار گرافیکی | Hewlett Packard HP-UX | Hyperion Solutions Hyperion System 9 Bi+ | IBM Cognos Business Intelligence | IBM Cognos Impromptu | IBM DB2 | IBM Domino | Informatica Corporation PowerCenter | JavaScript | Kubernetes | Linux | سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار کلان‌داده MapReduce | McAfee | MicroStrategy | MicroStrategy Desktop | Microsoft Access | Microsoft Active Directory | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | Microsoft Office Live Meeting | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Windows Server | Microsoft Word | نرم‌افزار خدمات دایرکتوری شبکه | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle Java | Oracle PeopleSoft | Oracle Solaris | PHP | Perl | پلتفرم به عنوان سرویس PaaS | Python | R | RESTful API | React | Ruby | SAP Adaptive Server Enterprise | SAP Business Objects | SAP Business One | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | نرم‌افزار تحلیل فروش | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی | زبان نشانه‌گذاری تایید امنیت SAML | Shell script | ورود یکباره SSO | نرم‌افزار به عنوان سرویس SaaS | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | Teradata Database | UNIX | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | WebEx Sales Center | Wireshark</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | تفکر انتقادی | درک نوشته‌ها | گوش دادن فعالانه | نگارش | یادگیری فعالانه | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | مهندسی و فناوری | زبان انگلیسی | ریاضیات | مدیریت و سازماندهی | طراحی | امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | زبان انگلیسی | ریاضیات | مدیریت و اداره | طراحی | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک نوشته‌ها | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بیان کتبی | حساسیت به مسئله | سازماندهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری طبقه‌بندی | بینایی نزدیک | اصالت | سهولت در کار با اعداد | استدلال ریاضی | سرعت بستار | حفظ کردن</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توانایی عددی | استدلال ریاضی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | محیط‌های داخلی و دارای کنترل دما | برخورد با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیمی | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق بودن یا بی‌نقص بودن | سطح رقابت | صرف زمان به صورت نشسته | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | سطح رقابت | صرف زمان برای نشستن | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aerospace Engineering and Operations Technologists and Technicians | Architectural and Engineering Managers | Commercial and Industrial Designers | Computer Systems Analysts | Computer Systems Engineers/Architects | Electrical Engineers | Electrical and Electronic Engineering Technologists and Technicians | Electronics Engineers, Except Computer | Industrial Engineering Technologists and Technicians | Industrial Engineers | Logistics Engineers | Manufacturing Engineers | Mechanical Engineering Technologists and Technicians | Mechanical Engineers | Project Management Specialists | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Software Developers | Solar Sales Representatives and Assessors</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مدیران معماری و مهندسی | طراحان تجاری و صنعتی | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | متخصصان مدیریت پروژه | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | توسعه‌دهندگان نرم‌افزار | نمایندگان و ارزیابان فروش تجهیزات خورشیدی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | گوش دادن فعالانه | درک نوشته‌ها | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و شخصی | زبان انگلیسی | مدیریت و سازماندهی | رایانه‌ها و الکترونیک | ارتباطات و رسانه</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک نوشته‌ها | توجه انتخابی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | درک کتبی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>گفتگوهای تلفنی | ارتباط با دیگران | صرف زمان به صورت نشسته | اهمیت دقیق بودن یا بی‌نقص بودن | محیط‌های داخلی و دارای کنترل دما | برخورد با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف مشابه | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویز که حواس‌پرت‌کننده یا آزاردهنده هستند | ایمیل | فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ایمیل | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Non-Retail Sales Workers | Market Research Analysts and Marketing Specialists | New Accounts Clerks | Order Clerks | Public Relations Specialists | Real Estate Sales Agents | Receptionists and Information Clerks | Retail Salespersons | Sales Managers | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Securities, Commodities, and Financial Services Sales Agents | Switchboard Operators, Including Answering Service | Telephone Operators</t>
+          <t>نمایندگان فروش تبلیغات | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | کارمندان حساب‌های جدید | کارمندان ثبت سفارش | متخصصان روابط عمومی | نمایندگان فروش املاک | متصدیان پذیرش و کارمندان اطلاعات | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | اپراتورهای تلفن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن‌ورزی | گوش دادن فعالانه | درک نوشته‌ها</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | زبان انگلیسی | امور اداری | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | سازماندهی اطلاعات | درک نوشته‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم | گفتگوهای تلفنی | ایمیل | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | نزدیکی فیزیکی</t>
+          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | ایمیل | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سخنرانی عمومی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Advertising Sales Agents | Baristas | Buyers and Purchasing Agents, Farm Products | Cashiers | Counter and Rental Clerks | Customer Service Representatives | Demonstrators and Product Promoters | Driver/Sales Workers | First-Line Supervisors of Retail Sales Workers | Merchandise Displayers and Window Trimmers | Order Clerks | Parts Salespersons | Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Shipping, Receiving, and Inventory Clerks | Stockers and Order Fillers | Telemarketers | Wholesale and Retail Buyers, Except Farm Products</t>
+          <t>نمایندگان فروش تبلیغات | باریستاها | خریداران و نمایندگان خرید، محصولات کشاورزی | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | رانندگان توزیع و فروشندگان | سرپرستان رده اول کارکنان فروش خرده‌فروشی | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | کارمندان ثبت سفارش | فروشندگان قطعات | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعالانه | سخن‌ورزی | درک نوشته‌ها | تفکر انتقادی | پایش | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و شخصی | زبان انگلیسی | مدیریت و سازماندهی | اقتصاد و حسابداری | رایانه‌ها و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | سازماندهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک نوشته‌ها | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | محیط‌های داخلی و دارای کنترل دما | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیمی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا بی‌نقص بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | سطح رقابت | سخنرانی عمومی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Retail Salespersons | Sales Representatives of Services, Except Advertising, Insurance, Financial Services, and Travel | Sales Representatives, Wholesale and Manufacturing, Except Technical and Scientific Products | Sales Representatives, Wholesale and Manufacturing, Technical and Scientific Products | Advertising Sales Agents | Insurance Sales Agents | Securities, Commodities, and Financial Services Sales Agents | Travel Agents | Real Estate Sales Agents | Real Estate Brokers | Sales Engineers | Telemarketers | Demonstrators and Product Promoters | Counter and Rental Clerks | Parts Salespersons | Solar Sales Representatives and Assessors | Door-to-Door Sales Workers, News and Street Vendors, and Related Workers | First-Line Supervisors of Retail Sales Workers | First-Line Supervisors of Non-Retail Sales Workers | Sales Managers</t>
+          <t>فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش تبلیغات | نمایندگان فروش بیمه | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | آژانس‌های مسافرتی | نمایندگان فروش املاک | کارگزاران املاک | مهندسان فروش | بازاریابان تلفنی | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | کارمندان باجه و اجاره | فروشندگان قطعات | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش خرده‌فروشی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | مدیران فروش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0064_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0064_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | طراحی | زبان انگلیسی | ریاضیات | مسکن و ساخت‌وساز | امور اداری و دفتری | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | طراحی | زبان انگلیسی | ریاضیات | ساختمان و ساخت‌وساز | اداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | دید نزدیک | دید دور | مرتب‌سازی اطلاعات | استدلال استقرایی | ابتکار و اصالت | انعطاف‌پذیری در نتیجه‌گیری | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | بینایی نزدیک | بینایی دور | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>معماران به‌جز معماری منظر و دریایی | مدیران معماری و مهندسی | مدیران ساخت‌وساز و پروژه‌های عمرانی | کارشناسان برآورد هزینه و مترورها | مهندسان برق | ممیزان انرژی | مهندسان انرژی به‌جز باد و خورشید | مدیران تولید انرژی زمین‌گرمایی | مهندسان فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | مدیران اجرایی و نصب سامانه‌های خورشیدی | مهندسان سامانه‌های انرژی خورشیدی | نصابان سامانه‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های سامانه‌های حرارتی خورشیدی | کارشناسان پایداری زیست‌محیطی | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران بهره‌برداری انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | مدیران فنی و مهندسی و معماری | مدیران پروژه‌های ساختمانی | کارشناسان برآورد هزینه و مترورها | مهندسان برق | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید انرژی زمین‌گرمایی | مهندسان فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | کارشناسان پایداری و توسعه پایدار | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | حمل‌ونقل و ترابری | رایانه و الکترونیک</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | حمل و نقل | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال استقرایی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | روانی ایده‌ها | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | خریداران و مأموران خرید محصولات کشاورزی | متصدیان پذیرش و اجاره کالا | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | کارشناسان لجستیک | کارمندان تدارکات و خرید | مأموران خرید به‌جز عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کاردان‌های انبار، تحویل و تحول کالا | کارگران انبار و چیدمان کالا | مدیران زنجیره تأمین | کارشناسان بازاریابی تلفنی | خریداران عمده و خرد به‌جز بخش کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | خریداران و کارشناسان خرید محصولات کشاورزی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | مدیران زنجیره تامین | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | صنایع غذایی و تولید خوراک | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | تولید مواد غذایی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | دید نزدیک | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک کتبی</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | صندوق‌داران | متصدیان پذیرش و اجاره کالا | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | رانندگان توزیع و پخش کالا | سرپرستان رده‌اول فروش غیرفروشگاهی | سرپرستان رده‌اول فروشگاه‌ها و خرده‌فروشی | راهنمایان و میزبانان سالن‌های پذیرایی | مدیران بازاریابی | کارشناسان برنامه‌ریزی همایش‌ها و رویدادها | طراحان چیدمان و دکوراسیون ویترین | فروشندگان قطعات یدکی | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کارگران انبار و چیدمان کالا | کارشناسان بازاریابی تلفنی | خریداران عمده و خرد به‌جز بخش کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | رانندگان توزیع و فروش مویرگی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | مدیران بازاریابی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | طراحان دکوراسیون و ویترین مغازه | فروشندگان قطعات و لوازم یدکی | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | علوم ارتباطات و رسانه | هنرهای تجسمی و زیبا | زبان انگلیسی | بازاریابی و فروش | طراحی</t>
+          <t>خدمات مشتری و شخصی | ارتباطات و رسانه | هنرهای زیبا | زبان انگلیسی | فروش و بازاریابی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | دید دور | هماهنگی کل بدن | تعادل بدنی | استقامت بدنی | دامنه انعطاف‌پذیری بدن | حافظه و به‌خاطرسپاری | حساسیت به مسئله | ابتکار و اصالت | مرتب‌سازی اطلاعات | تشخیص گفتار | توجه انتخابی | هماهنگی چند اندام | قدرت تنه | انعطاف‌پذیری پویا</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | بینایی دور | هماهنگی کلی بدن | تعادل کلی بدن | استقامت | انعطاف‌پذیری دامنه حرکت | حفظ کردن | حساسیت به مسئله | اصالت | ترتیب‌دهی اطلاعات | تشخیص گفتار | توجه انتخابی | هماهنگی چند عضو | قدرت تنه | انعطاف‌پذیری پویا</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>حفظ فیگور و ژست در محیط‌های استودیویی | تعامل و هماهنگی نزدیک با گروه تصویربرداری و طراحان | محیط سرپوشیده با تهویهٔ مطبوع | حفظ انضباط فیزیکی و ظاهری در طول جلسات کاری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازیگران | مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | مسئولان لباس و تن‌پوش | هنرمندان صنایع دستی | هنرمندان رقص و حرکات موزون | معرفی‌کنندگان و مروجان کالا | طراحان لباس و مد | نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | چهره‌پردازان و گریمورهای تئاتر و سینما | طراحان چیدمان و دکوراسیون ویترین | ماکت‌سازان چوبی | رنگ‌کاران و تزیین‌کاران | عکاسان | متصدیان لابراتوار و چاپ عکس | طراحان صحنه و دکور | پویانماها و طراحان جلوه‌های ویژه | مدیران انتخاب بازیگر و چهره‌یابی</t>
+          <t>بازیگران | مدیران هنری | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | متصدیان و جامه داران لباس صحنه | هنرمندان صنایع دستی | هنرمندان رقص و حرکات موزون | معرفی‌کنندگان و مروجان کالا | طراحان مد و پوشاک | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | چهره‌پردازان و گریموران تئاتر و سینما | طراحان دکوراسیون و ویترین مغازه | مدل‌سازان چوب | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | عکاسان | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | طراحان صحنه و نمایشگاه | پویانماها و طراحان جلوه‌های ویژه | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | نگارش | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | حقوق و امور دولتی | مدیریت و امور اداری | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | علوم ارتباطات و رسانه | مسکن و ساخت‌وساز | امور اداری و دفتری | آموزش و تدریس | روان‌شناسی</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری | رایانه و الکترونیک | ریاضیات | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | دید نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان رسمی املاک | ارزیابان اموال شخصی و تجاری | متصدیان امور دفتری کارگزاری | متصدیان پذیرش و اجاره کالا | تحلیل‌گران مالی و اعتباری | کارشناسان اعتبارسنجی و بررسی تسهیلات | مشاوران اعتباری و تسهیلاتی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش بیمه | مصاحبه‌گران و متصدیان پرونده‌های وام | کارشناسان و مسئولان اعطای وام | متصدیان افتتاح حساب | مشاوران مالی شخصی | مدیران مجتمع‌های مسکونی، تجاری و املاک | مأموران خرید به‌جز عمده‌فروشی، خرده‌فروشی و کشاورزی | مشاوران و کارشناسان فروش املاک | مدیران فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارگزاران و معامله‌گران بورس، اوراق بهادار و کالا | خریداران عمده و خرد به‌جز بخش کشاورزی</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | کارشناسان امور اداری و معاملات کارگزاری | متصدیان باجه و کرایه کالا و خدمات | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی فردی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید و امور قراردادها | مشاوران و کارشناسان فروش املاک | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | حقوق و امور دولتی | امور اداری و دفتری | مدیریت و امور اداری | ریاضیات | رایانه و الکترونیک | علوم ارتباطات و رسانه | مسکن و ساخت‌وساز | اقتصاد و حسابداری | آموزش و تدریس | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | قانون و دولت | اداری | مدیریت و اداره | ریاضیات | رایانه و الکترونیک | ارتباطات و رسانه | ساختمان و ساخت‌وساز | اقتصاد و حسابداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | دید دور | انعطاف‌پذیری در نتیجه‌گیری | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | ارزیابان و کارشناسان رسمی املاک | ارزیابان اموال شخصی و تجاری | متصدیان امور دفتری کارگزاری | متصدیان پذیرش و اجاره کالا | مشاوران اعتباری و تسهیلاتی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش بیمه | مصاحبه‌گران و متصدیان پرونده‌های وام | کارشناسان و مسئولان اعطای وام | متصدیان افتتاح حساب | مشاوران مالی شخصی | مدیران مجتمع‌های مسکونی، تجاری و املاک | مأموران خرید به‌جز عمده‌فروشی، خرده‌فروشی و کشاورزی | کارگزاران و مدیران معاملات املاک | مدیران فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارگزاران و معامله‌گران بورس، اوراق بهادار و کالا | کارشناسان بازاریابی تلفنی | خریداران عمده و خرد به‌جز بخش کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | کارشناسان امور اداری و معاملات کارگزاری | متصدیان باجه و کرایه کالا و خدمات | مشاوران اعتباری و مدیریت بدهی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی فردی | مدیران املاک، مستغلات و مجتمع‌های مسکونی | کارشناسان خرید و امور قراردادها | کارگزاران و مدیران معاملات املاک | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | مهندسی و فناوری | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | طراحی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | زبان انگلیسی | ریاضیات | مدیریت و اداره | طراحی | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | ابتکار و اصالت | محاسبات عددی | استدلال ریاضی | سرعت در نتیجه‌گیری | حافظه و به‌خاطرسپاری</t>
+          <t>بیان شفاهی | وضوح گفتار | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | اصالت | توانایی عددی | استدلال ریاضی | سرعت بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مدیران معماری و مهندسی | طراحان تجاری و صنعتی | تحلیل‌گران سامانه‌های رایانه‌ای | معماران و مهندسان سامانه‌های رایانه‌ای | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک به‌جز رایانه | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک | مهندسان تولید و ساخت | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان مدیریت پروژه | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | توسعه‌دهندگان نرم‌افزار | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مدیران فنی و مهندسی و معماری | طراحان تجاری و صنعتی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | کارشناسان مدیریت پروژه | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | توسعه‌دهندگان نرم‌افزار | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | علوم ارتباطات و رسانه</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | صندوق‌داران | متصدیان پذیرش و اجاره کالا | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروش غیرفروشگاهی | کارشناسان تحقیقات بازار و متخصصان بازاریابی | متصدیان افتتاح حساب | کارمندان ثبت و پیگیری سفارش‌ها | کارشناسان روابط عمومی | مشاوران و کارشناسان فروش املاک | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کارگزاران و معامله‌گران بورس، اوراق بهادار و کالا | اپراتورهای تلفن‌خانه و مراکز پاسخ‌گویی | متصدیان تلفن و اپراتورها</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | متصدیان افتتاح حساب | متصدیان ثبت و پیگیری سفارش‌ها | کارشناسان روابط عمومی | مشاوران و کارشناسان فروش املاک | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | اپراتورهای مراکز تلفن و پاسخگویی | اپراتورهای تلفن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزارهای مسیریابی و نقشه‌خوانی | نرم‌افزار مدیریت فایل‌ها در گوشی هوشمند | نرم‌افزار مرورگر وب | Microsoft Excel | شبکه‌های اجتماعی</t>
+          <t>Facebook | نرم‌افزار مدیریت فایل‌ها در گوشی هوشمند | نرم‌افزار Microsoft Office | نرم‌افزار نقشه‌برداری مسیر | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | زبان انگلیسی | امور اداری و دفتری | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | اداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | مرتب‌سازی اطلاعات | درک کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | بیان کتبی | ترتیب‌دهی اطلاعات | درک کتبی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارگزاران فروش تبلیغات | باریستاها | خریداران و مأموران خرید محصولات کشاورزی | صندوق‌داران | متصدیان پذیرش و اجاره کالا | کارشناسان خدمات پس از فروش و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | رانندگان توزیع و پخش کالا | سرپرستان رده‌اول فروشگاه‌ها و خرده‌فروشی | طراحان چیدمان و دکوراسیون ویترین | کارمندان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات یدکی | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کاردان‌های انبار، تحویل و تحول کالا | کارگران انبار و چیدمان کالا | کارشناسان بازاریابی تلفنی | خریداران عمده و خرد به‌جز بخش کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | باریستاها | خریداران و کارشناسان خرید محصولات کشاورزی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | رانندگان توزیع و فروش مویرگی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان دکوراسیون و ویترین مغازه | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>بازاریابی و فروش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | اقتصاد و حسابداری | رایانه و الکترونیک | علوم ارتباطات و رسانه | ریاضیات</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | رایانه و الکترونیک | ارتباطات و رسانه | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | اشتراک زمانی | چابکی انگشتان | چابکی دستی | دید دور | حافظه و به‌خاطرسپاری | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>فروشندگان خرده‌فروشی | کارشناسان فروش خدمات به‌جز تبلیغات، بیمه، مالی و گردشگری | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و تولیدی محصولات فنی و علمی | کارگزاران فروش تبلیغات | کارشناسان فروش بیمه | کارگزاران و معامله‌گران بورس، اوراق بهادار و کالا | کارشناسان فروش تور و آژانس‌های مسافرتی | مشاوران و کارشناسان فروش املاک | کارگزاران و مدیران معاملات املاک | مهندسان فروش | کارشناسان بازاریابی تلفنی | معرفی‌کنندگان و مروجان کالا | متصدیان پذیرش و اجاره کالا | فروشندگان قطعات یدکی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشگاه‌ها و خرده‌فروشی | سرپرستان رده‌اول فروش غیرفروشگاهی | مدیران فروش</t>
+          <t>فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش فضاهای تبلیغاتی | نمایندگان و کارشناسان فروش بیمه | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | مشاوران و کارشناسان فروش املاک | کارگزاران و مدیران معاملات املاک | مهندسان فروش | کارشناسان بازاریابی تلفنی | معرفی‌کنندگان و مروجان کالا | متصدیان باجه و کرایه کالا و خدمات | فروشندگان قطعات و لوازم یدکی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | مدیران فروش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
